--- a/PROVENANCE-MATRIX-FW410.xlsx
+++ b/PROVENANCE-MATRIX-FW410.xlsx
@@ -1017,7 +1017,7 @@
     <row r="2">
       <c r="A2" s="78" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D6" s="70" t="inlineStr">
         <is>
-          <t>0.4.0 Classic (driver 0.3.0, painel 1.6) instalado no iMac com o FW410: attach, todas as saídas (44.1-192), gravação, latência, stereo pairs, mixer, encoder, volume de fones (capturas 105-106). Bit 5 dos fones = aux (desvio R138).</t>
+          <t>v0.4.1 publicado (Classic + Modern; driver 0.3.1, painel 1.6): stereo pairs com canais em qualquer taxa (R141, verificado no dev Mac com o 1814 a 48 kHz). README simplificado: os três modelos e todos os recursos como suportados (usuário).</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D11" s="70" t="inlineStr">
         <is>
-          <t>Pendente (sob decisão do usuário): MIDI, S/PDIF/sync externo, óptico, sleep/wake; vazamento FWHsci no kextunload (R138); edição Modern; README/release.</t>
+          <t>Pendente (sob decisão do usuário): MIDI, S/PDIF/sync externo, óptico, sleep/wake com o 410.</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="51" min="1" max="1"/>
@@ -4111,7 +4111,85 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="22.35" customHeight="1" s="21"/>
+    <row r="24" ht="22.35" customHeight="1" s="21">
+      <c r="A24" s="51" t="inlineStr">
+        <is>
+          <t>410-0.6.2</t>
+        </is>
+      </c>
+      <c r="B24" s="51" t="inlineStr">
+        <is>
+          <t>410-0.6</t>
+        </is>
+      </c>
+      <c r="C24" s="51" t="inlineStr">
+        <is>
+          <t>Pair streams sem formato fora de 44.1 kHz</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="inlineStr">
+        <is>
+          <t>IOAudioStream::setFormat valida contra a taxa ATUAL do engine; ResetIOFormat (ordem da ref @0x1ab42) fixava a taxa depois -&gt; pair devices sem canais a 48 kHz+ no macOS 14</t>
+        </is>
+      </c>
+      <c r="E24" s="51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F24" s="51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G24" s="51" t="inlineStr">
+        <is>
+          <t>otool + fonte IOAudioFamily</t>
+        </is>
+      </c>
+      <c r="H24" s="51" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I24" s="51" t="inlineStr">
+        <is>
+          <t>IOAudioFamily 540.3 IOAudioStream.cpp:262-268;captura 107;captura 106 (44.1 kHz);ref @0x1ab42</t>
+        </is>
+      </c>
+      <c r="J24" s="51">
+        <f>IF(TRIM(I24)="",0,LEN(I24)-LEN(SUBSTITUTE(I24,";",""))+1)</f>
+        <v/>
+      </c>
+      <c r="K24" s="51" t="inlineStr">
+        <is>
+          <t>Corrigido 2026-10-27</t>
+        </is>
+      </c>
+      <c r="L24" s="51">
+        <f>ROUND(IF(H24="Sim",MIN(Legenda!$C$12,MIN(10,IF(E24="Sim",Legenda!$C$4,IF(E24="Parcial",Legenda!$C$5,0))+IF(F24="Sim",Legenda!$C$6,IF(F24="Parcial",Legenda!$C$7,0))+IF(G24="otool + Ghidra",Legenda!$C$8,IF(OR(G24="otool",G24="Ghidra",G24="Outro binário"),Legenda!$C$9,0))+MIN(Legenda!$C$11,MAX(0,J24-1)*Legenda!$C$10))),IF(H24="Parcial",MIN(Legenda!$C$13,MIN(10,IF(E24="Sim",Legenda!$C$4,IF(E24="Parcial",Legenda!$C$5,0))+IF(F24="Sim",Legenda!$C$6,IF(F24="Parcial",Legenda!$C$7,0))+IF(G24="otool + Ghidra",Legenda!$C$8,IF(OR(G24="otool",G24="Ghidra",G24="Outro binário"),Legenda!$C$9,0))+MIN(Legenda!$C$11,MAX(0,J24-1)*Legenda!$C$10))),MIN(10,IF(E24="Sim",Legenda!$C$4,IF(E24="Parcial",Legenda!$C$5,0))+IF(F24="Sim",Legenda!$C$6,IF(F24="Parcial",Legenda!$C$7,0))+IF(G24="otool + Ghidra",Legenda!$C$8,IF(OR(G24="otool",G24="Ghidra",G24="Outro binário"),Legenda!$C$9,0))+MIN(Legenda!$C$11,MAX(0,J24-1)*Legenda!$C$10)))),1)</f>
+        <v/>
+      </c>
+      <c r="M24" s="51" t="inlineStr">
+        <is>
+          <t>PROVENANCE-RESOLUTIONS R141; captura 107</t>
+        </is>
+      </c>
+      <c r="N24" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O24" s="51" t="inlineStr">
+        <is>
+          <t>[2026-10-27] corrigido no driver 0.3.1 (setSampleRate antes do setFormat); verificado no dev Mac com o 1814 a 48 kHz (captura 107 after-0.4.1-*); outras taxas não vistas</t>
+        </is>
+      </c>
+      <c r="P24" s="51">
+        <f>LEFT(A24,FIND(".",A24&amp;".")-1)</f>
+        <v/>
+      </c>
+    </row>
     <row r="25" ht="22.35" customHeight="1" s="21"/>
     <row r="26" ht="22.35" customHeight="1" s="21"/>
     <row r="27" ht="22.35" customHeight="1" s="21"/>
@@ -4288,7 +4366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="21" min="1" max="1"/>
@@ -5567,7 +5645,7 @@
       </c>
       <c r="I27" s="51" t="inlineStr">
         <is>
-          <t>[2026-10-26] [2026-10-26 late] pares ok no 410; 1814 o usuário testa</t>
+          <t>[2026-10-26] [2026-10-26 late] pares ok no 410; 1814 o usuário testa [2026-10-27] 1814 a 48 kHz (Modern): pair devices sem canais; causa no kext (R141, B-7); o teste do 410 foi a 44.1 kHz</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5833,7 @@
       </c>
       <c r="I31" s="51" t="inlineStr">
         <is>
-          <t>[2026-10-26] [2026-10-26 late] pkg Classic instalado; Modern, README, release pendentes</t>
+          <t>[2026-10-26] [2026-10-26 late] pkg Classic instalado; Modern, README, release pendentes [2026-10-27] v0.4.1 (Classic + Modern) construído e publicado; README simplificado (usuário)</t>
         </is>
       </c>
     </row>
@@ -5803,6 +5881,53 @@
       <c r="I32" s="51" t="inlineStr">
         <is>
           <t>[2026-10-26] [2026-10-26 late] captura 106; falta MIDI, S/PDIF, sleep/wake</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>B-7</t>
+        </is>
+      </c>
+      <c r="B33" s="51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="51" t="inlineStr">
+        <is>
+          <t>Pair engine: taxa antes do setFormat (R141)</t>
+        </is>
+      </c>
+      <c r="D33" s="51" t="inlineStr">
+        <is>
+          <t>canais nos pair devices a 48 kHz (CoreAudio) + IOAudioStreamFormat em cada FWPairStream</t>
+        </is>
+      </c>
+      <c r="E33" s="51" t="inlineStr">
+        <is>
+          <t>B-6</t>
+        </is>
+      </c>
+      <c r="F33" s="51" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="G33" s="51" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H33" s="51" t="inlineStr">
+        <is>
+          <t>R141</t>
+        </is>
+      </c>
+      <c r="I33" s="51" t="inlineStr">
+        <is>
+          <t>[2026-10-27] pacote 0.4.1 Modern instalado no dev Mac: 14/14 pair streams com formato, todos os pair devices com canais a 48 kHz (captura 107, usuário); publicado em v0.4.1</t>
         </is>
       </c>
     </row>
